--- a/GWD Data/PVC With Trench.xlsx
+++ b/GWD Data/PVC With Trench.xlsx
@@ -95,7 +95,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -105,24 +105,13 @@
     <font>
       <b/>
       <sz val="12.0"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Merriweather"/>
     </font>
     <font/>
     <font>
-      <b/>
       <sz val="12.0"/>
       <color theme="1"/>
-      <name val="Merriweather"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Merriweather"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color rgb="FF000000"/>
       <name val="Merriweather"/>
     </font>
   </fonts>
@@ -262,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -271,67 +260,64 @@
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="3" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="3" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="3" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="4" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -548,7 +534,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
-    <tabColor rgb="FF00FF00"/>
+    <tabColor rgb="FFFF00FF"/>
     <pageSetUpPr/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
@@ -636,10 +622,10 @@
       <c r="D6" s="13">
         <v>11.5</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="11">
         <v>475.0</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="14">
         <f>D6*E6</f>
         <v>5462.5</v>
       </c>
@@ -655,100 +641,100 @@
       <c r="F7" s="10"/>
     </row>
     <row r="8">
-      <c r="A8" s="16"/>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <f>F6*0.01</f>
         <v>54.625</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16"/>
-      <c r="B9" s="17" t="s">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="7"/>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <f>SUM(F6:F8)</f>
         <v>5517.125</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16"/>
-      <c r="B10" s="17" t="s">
+      <c r="A10" s="15"/>
+      <c r="B10" s="16" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <f>F9*0.15</f>
         <v>827.56875</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="16"/>
-      <c r="B11" s="17" t="s">
+      <c r="A11" s="15"/>
+      <c r="B11" s="16" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <f>SUM(F9:F10)</f>
         <v>6344.69375</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="15"/>
+      <c r="B12" s="16" t="s">
         <v>17</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <f>F11</f>
         <v>6344.69375</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17" t="s">
+      <c r="A13" s="15"/>
+      <c r="B13" s="16" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="19">
+      <c r="F13" s="18">
         <f>round(F12/10,2)</f>
         <v>634.47</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16">
+      <c r="A14" s="15">
         <v>116.0</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D14" s="15">
         <v>0.12</v>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="19">
         <v>784.0</v>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="17">
         <f t="shared" ref="F14:F15" si="1">D14*E14</f>
         <v>94.08</v>
       </c>
@@ -766,10 +752,10 @@
       <c r="D15" s="13">
         <v>0.25</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="11">
         <v>645.0</v>
       </c>
-      <c r="F15" s="21">
+      <c r="F15" s="20">
         <f t="shared" si="1"/>
         <v>161.25</v>
       </c>
@@ -797,128 +783,128 @@
       <c r="D17" s="13">
         <v>0.66</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E17" s="11">
         <v>645.0</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="20">
         <f t="shared" ref="F17:F18" si="2">D17*E17</f>
         <v>425.7</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="22">
+      <c r="A18" s="21">
         <v>115.0</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="21">
         <v>0.66</v>
       </c>
-      <c r="E18" s="24">
+      <c r="E18" s="23">
         <v>645.0</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="24">
         <f t="shared" si="2"/>
         <v>425.7</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="23"/>
-      <c r="B19" s="26" t="s">
+      <c r="A19" s="22"/>
+      <c r="B19" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="25">
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="27"/>
+      <c r="F19" s="24">
         <f>SUM(F14:F18)</f>
         <v>1106.73</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="23"/>
-      <c r="B20" s="26" t="s">
+      <c r="A20" s="22"/>
+      <c r="B20" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="25">
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="27"/>
+      <c r="F20" s="24">
         <f>F19*0.01</f>
         <v>11.0673</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="23"/>
-      <c r="B21" s="26" t="s">
+      <c r="A21" s="22"/>
+      <c r="B21" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="25">
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="24">
         <f>SUM(F19:F20)</f>
         <v>1117.7973</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="23"/>
-      <c r="B22" s="26" t="s">
+      <c r="A22" s="22"/>
+      <c r="B22" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="25">
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="27"/>
+      <c r="F22" s="24">
         <f>F21*0.15</f>
         <v>167.669595</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="23"/>
-      <c r="B23" s="26" t="s">
+      <c r="A23" s="22"/>
+      <c r="B23" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="25">
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="27"/>
+      <c r="F23" s="24">
         <f>SUM(F21:F22)</f>
         <v>1285.466895</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="23"/>
-      <c r="B24" s="26" t="s">
+      <c r="A24" s="22"/>
+      <c r="B24" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="25">
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="27"/>
+      <c r="F24" s="24">
         <f>F23</f>
         <v>1285.466895</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="23"/>
-      <c r="B25" s="26" t="s">
+      <c r="A25" s="22"/>
+      <c r="B25" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="19">
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="27"/>
+      <c r="F25" s="18">
         <f>round(F24/10,2)</f>
         <v>128.55</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="29" t="str">
+      <c r="A26" s="28" t="str">
         <f>CONCATENATE("Say ₹ ",F13," + ",F25," x Cost Index")</f>
         <v>Say ₹ 634.47 + 128.55 x Cost Index</v>
       </c>

--- a/GWD Data/PVC With Trench.xlsx
+++ b/GWD Data/PVC With Trench.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="28">
   <si>
     <t>PVC Pipe With Trenching</t>
   </si>
@@ -86,6 +86,15 @@
   </si>
   <si>
     <t>TOTAL  </t>
+  </si>
+  <si>
+    <t>Providing and fixing PVC pipes includes jointing of pipes with one step PVC solvent cement, trenching, refilling &amp; testing of joints complete as per direction of Engineer in Charge. 63 mm dia 10 KGF/cm2</t>
+  </si>
+  <si>
+    <t>MR10234</t>
+  </si>
+  <si>
+    <t>PVC Pipe, 10kg/cm2, 63mm Dia.</t>
   </si>
 </sst>
 </file>
@@ -115,7 +124,7 @@
       <name val="Merriweather"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -132,6 +141,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
         <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAD1DC"/>
+        <bgColor rgb="FFEAD1DC"/>
       </patternFill>
     </fill>
   </fills>
@@ -251,7 +266,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="49">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -323,6 +338,66 @@
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="5" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="8" fillId="4" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="10" fillId="4" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -543,7 +618,7 @@
     <col customWidth="1" min="2" max="2" width="32.75"/>
     <col customWidth="1" min="3" max="3" width="6.75"/>
     <col customWidth="1" min="4" max="4" width="9.75"/>
-    <col customWidth="1" min="5" max="5" width="6.0"/>
+    <col customWidth="1" min="5" max="5" width="7.0"/>
     <col customWidth="1" min="6" max="6" width="12.88"/>
   </cols>
   <sheetData>
@@ -914,8 +989,392 @@
       <c r="E26" s="2"/>
       <c r="F26" s="3"/>
     </row>
+    <row r="27">
+      <c r="A27" s="29">
+        <v>0.0</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="B28" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28" s="29" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="31"/>
+      <c r="B29" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10"/>
+      <c r="B30" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>12</v>
+      </c>
+      <c r="D31" s="35">
+        <v>11.5</v>
+      </c>
+      <c r="E31" s="33">
+        <v>150.0</v>
+      </c>
+      <c r="F31" s="36">
+        <f>D31*E31</f>
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10"/>
+      <c r="B32" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="10"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="37"/>
+      <c r="B33" s="38" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="39">
+        <f>F31*0.01</f>
+        <v>17.25</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="37"/>
+      <c r="B34" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="6"/>
+      <c r="D34" s="6"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="39">
+        <f>SUM(F31:F33)</f>
+        <v>1742.25</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="37"/>
+      <c r="B35" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="6"/>
+      <c r="D35" s="6"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="39">
+        <f>F34*0.15</f>
+        <v>261.3375</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="37"/>
+      <c r="B36" s="38" t="s">
+        <v>15</v>
+      </c>
+      <c r="C36" s="6"/>
+      <c r="D36" s="6"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="39">
+        <f>SUM(F34:F35)</f>
+        <v>2003.5875</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="37"/>
+      <c r="B37" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="C37" s="6"/>
+      <c r="D37" s="6"/>
+      <c r="E37" s="7"/>
+      <c r="F37" s="39">
+        <f>F36</f>
+        <v>2003.5875</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="37"/>
+      <c r="B38" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="6"/>
+      <c r="D38" s="6"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="40">
+        <f>round(F37/10,2)</f>
+        <v>200.36</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="37">
+        <v>116.0</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C39" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" s="37">
+        <v>0.12</v>
+      </c>
+      <c r="E39" s="41">
+        <v>784.0</v>
+      </c>
+      <c r="F39" s="39">
+        <f t="shared" ref="F39:F40" si="3">D39*E39</f>
+        <v>94.08</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="35">
+        <v>114.0</v>
+      </c>
+      <c r="B40" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" s="35">
+        <v>0.25</v>
+      </c>
+      <c r="E40" s="33">
+        <v>645.0</v>
+      </c>
+      <c r="F40" s="42">
+        <f t="shared" si="3"/>
+        <v>161.25</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10"/>
+      <c r="B41" s="32" t="s">
+        <v>22</v>
+      </c>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="10"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="35">
+        <v>114.0</v>
+      </c>
+      <c r="B42" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="C42" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D42" s="35">
+        <v>0.66</v>
+      </c>
+      <c r="E42" s="33">
+        <v>645.0</v>
+      </c>
+      <c r="F42" s="42">
+        <f t="shared" ref="F42:F43" si="4">D42*E42</f>
+        <v>425.7</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="43">
+        <v>115.0</v>
+      </c>
+      <c r="B43" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" s="43">
+        <v>0.66</v>
+      </c>
+      <c r="E43" s="45">
+        <v>645.0</v>
+      </c>
+      <c r="F43" s="46">
+        <f t="shared" si="4"/>
+        <v>425.7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="44"/>
+      <c r="B44" s="47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="27"/>
+      <c r="F44" s="46">
+        <f>SUM(F39:F43)</f>
+        <v>1106.73</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="44"/>
+      <c r="B45" s="47" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="27"/>
+      <c r="F45" s="46">
+        <f>F44*0.01</f>
+        <v>11.0673</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="44"/>
+      <c r="B46" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="27"/>
+      <c r="F46" s="46">
+        <f>SUM(F44:F45)</f>
+        <v>1117.7973</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="44"/>
+      <c r="B47" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" s="26"/>
+      <c r="D47" s="26"/>
+      <c r="E47" s="27"/>
+      <c r="F47" s="46">
+        <f>F46*0.15</f>
+        <v>167.669595</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="44"/>
+      <c r="B48" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="26"/>
+      <c r="D48" s="26"/>
+      <c r="E48" s="27"/>
+      <c r="F48" s="46">
+        <f>SUM(F46:F47)</f>
+        <v>1285.466895</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="44"/>
+      <c r="B49" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="46">
+        <f>F48</f>
+        <v>1285.466895</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="44"/>
+      <c r="B50" s="47" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="27"/>
+      <c r="F50" s="40">
+        <f>round(F49/10,2)</f>
+        <v>128.55</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="48" t="str">
+        <f>CONCATENATE("Say ₹ ",F38," + ",F50," x Cost Index")</f>
+        <v>Say ₹ 200.36 + 128.55 x Cost Index</v>
+      </c>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="61">
+    <mergeCell ref="A29:A30"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="F29:F30"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="C31:C32"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="B47:E47"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B49:E49"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B45:E45"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="D6:D7"/>
@@ -934,12 +1393,6 @@
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B12:E12"/>
     <mergeCell ref="B13:E13"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="B23:E23"/>
-    <mergeCell ref="B24:E24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="A26:F26"/>
     <mergeCell ref="A15:A16"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="D15:D16"/>
@@ -947,6 +1400,15 @@
     <mergeCell ref="F15:F16"/>
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="B23:E23"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="B27:F27"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/GWD Data/PVC With Trench.xlsx
+++ b/GWD Data/PVC With Trench.xlsx
@@ -1,12 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="240" yWindow="120" windowWidth="14940" windowHeight="9225" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name=" PVC With Trench" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -100,28 +104,36 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="177" formatCode="0.000"/>
   </numFmts>
   <fonts count="4">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Merriweather"/>
+      <name val="Cambria"/>
+      <family val="2"/>
     </font>
-    <font/>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Merriweather"/>
+      <name val="Cambria"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -129,33 +141,40 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D2E9"/>
-        <bgColor rgb="FFD9D2E9"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEAD1DC"/>
-        <bgColor rgb="FFEAD1DC"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="11">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -164,6 +183,8 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
@@ -172,6 +193,7 @@
       </bottom>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -200,6 +222,7 @@
       <left style="thin">
         <color rgb="FF3D3D3D"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF3D3D3D"/>
       </top>
@@ -208,6 +231,8 @@
       </bottom>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF3D3D3D"/>
       </top>
@@ -216,6 +241,7 @@
       </bottom>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF3D3D3D"/>
       </right>
@@ -236,6 +262,7 @@
       <top style="thin">
         <color rgb="FF3D3D3D"/>
       </top>
+      <bottom/>
     </border>
     <border>
       <left style="thin">
@@ -244,6 +271,7 @@
       <right style="thin">
         <color rgb="FF3D3D3D"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF3D3D3D"/>
       </bottom>
@@ -263,206 +291,370 @@
       </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="3" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="3" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="5" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="3" numFmtId="2" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="8" fillId="4" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="10" fillId="4" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+  <cellXfs count="39">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="4" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="6">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="15" builtinId="5"/>
+    <cellStyle name="Currency" xfId="16" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="17" builtinId="7"/>
+    <cellStyle name="Comma" xfId="18" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="19" builtinId="6"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="000000"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="FFFFFF"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4285F4"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="EA4335"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="FBBC04"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="34A853"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="FF6D01"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="46BDC6"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -603,26 +795,22 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <tabColor rgb="FFFF00FF"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="6.88"/>
-    <col customWidth="1" min="2" max="2" width="32.75"/>
-    <col customWidth="1" min="3" max="3" width="6.75"/>
-    <col customWidth="1" min="4" max="4" width="9.75"/>
-    <col customWidth="1" min="5" max="5" width="7.0"/>
-    <col customWidth="1" min="6" max="6" width="12.88"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A751D6-6F22-48F9-BA03-042F37A8B9A6}">
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:6" ht="12.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -632,9 +820,9 @@
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:6" ht="12.75">
       <c r="A2" s="4">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>1</v>
@@ -644,7 +832,7 @@
       <c r="E2" s="6"/>
       <c r="F2" s="7"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:6" ht="12.75">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -664,7 +852,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:6" ht="12.75">
       <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
         <v>8</v>
@@ -674,7 +862,7 @@
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:6" ht="12.75">
       <c r="A5" s="10"/>
       <c r="B5" s="9" t="s">
         <v>9</v>
@@ -684,28 +872,28 @@
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:6" ht="12.75">
       <c r="A6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="13">
-        <v>11.5</v>
+      <c r="D6" s="11">
+        <v>11.50</v>
       </c>
       <c r="E6" s="11">
-        <v>475.0</v>
-      </c>
-      <c r="F6" s="14">
+        <v>475</v>
+      </c>
+      <c r="F6" s="12">
         <f>D6*E6</f>
-        <v>5462.5</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>5462.50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="12.75">
       <c r="A7" s="10"/>
       <c r="B7" s="9" t="s">
         <v>13</v>
@@ -715,127 +903,127 @@
       <c r="E7" s="10"/>
       <c r="F7" s="10"/>
     </row>
-    <row r="8">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16" t="s">
+    <row r="8" spans="1:6" ht="12.75">
+      <c r="A8" s="13"/>
+      <c r="B8" s="14" t="s">
         <v>14</v>
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="17">
+      <c r="F8" s="15">
         <f>F6*0.01</f>
         <v>54.625</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="15"/>
-      <c r="B9" s="16" t="s">
+    <row r="9" spans="1:6" ht="12.75">
+      <c r="A9" s="13"/>
+      <c r="B9" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="6"/>
       <c r="D9" s="6"/>
       <c r="E9" s="7"/>
-      <c r="F9" s="17">
+      <c r="F9" s="15">
         <f>SUM(F6:F8)</f>
         <v>5517.125</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="15"/>
-      <c r="B10" s="16" t="s">
+    <row r="10" spans="1:6" ht="12.75">
+      <c r="A10" s="13"/>
+      <c r="B10" s="14" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="E10" s="7"/>
-      <c r="F10" s="17">
+      <c r="F10" s="15">
         <f>F9*0.15</f>
-        <v>827.56875</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15"/>
-      <c r="B11" s="16" t="s">
+        <v>827.56875000000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="12.75">
+      <c r="A11" s="13"/>
+      <c r="B11" s="14" t="s">
         <v>15</v>
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="17">
+      <c r="F11" s="15">
         <f>SUM(F9:F10)</f>
-        <v>6344.69375</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15"/>
-      <c r="B12" s="16" t="s">
+        <v>6344.6937500000004</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="12.75">
+      <c r="A12" s="13"/>
+      <c r="B12" s="14" t="s">
         <v>17</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="17">
+      <c r="F12" s="15">
         <f>F11</f>
-        <v>6344.69375</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15"/>
-      <c r="B13" s="16" t="s">
+        <v>6344.6937500000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="12.75">
+      <c r="A13" s="13"/>
+      <c r="B13" s="14" t="s">
         <v>18</v>
       </c>
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="7"/>
-      <c r="F13" s="18">
-        <f>round(F12/10,2)</f>
+      <c r="F13" s="16">
+        <f>ROUND(F12/10,2)</f>
         <v>634.47</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="15">
-        <v>116.0</v>
+    <row r="14" spans="1:6" ht="12.75">
+      <c r="A14" s="13">
+        <v>116</v>
       </c>
       <c r="B14" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="15">
+      <c r="D14" s="13">
         <v>0.12</v>
       </c>
-      <c r="E14" s="19">
-        <v>784.0</v>
-      </c>
-      <c r="F14" s="17">
-        <f t="shared" ref="F14:F15" si="1">D14*E14</f>
+      <c r="E14" s="13">
+        <v>784</v>
+      </c>
+      <c r="F14" s="15">
+        <f>D14*E14</f>
         <v>94.08</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13">
-        <v>114.0</v>
+    <row r="15" spans="1:6" ht="12.75">
+      <c r="A15" s="11">
+        <v>114</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D15" s="11">
         <v>0.25</v>
       </c>
       <c r="E15" s="11">
-        <v>645.0</v>
-      </c>
-      <c r="F15" s="20">
-        <f t="shared" si="1"/>
+        <v>645</v>
+      </c>
+      <c r="F15" s="17">
+        <f>D15*E15</f>
         <v>161.25</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:6" ht="12.75">
       <c r="A16" s="10"/>
       <c r="B16" s="9" t="s">
         <v>22</v>
@@ -845,141 +1033,141 @@
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
     </row>
-    <row r="17">
-      <c r="A17" s="13">
-        <v>114.0</v>
+    <row r="17" spans="1:6" ht="12.75">
+      <c r="A17" s="11">
+        <v>114</v>
       </c>
       <c r="B17" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="11">
         <v>0.66</v>
       </c>
       <c r="E17" s="11">
-        <v>645.0</v>
-      </c>
-      <c r="F17" s="20">
-        <f t="shared" ref="F17:F18" si="2">D17*E17</f>
-        <v>425.7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21">
-        <v>115.0</v>
-      </c>
-      <c r="B18" s="22" t="s">
+        <v>645</v>
+      </c>
+      <c r="F17" s="17">
+        <f>D17*E17</f>
+        <v>425.70</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="12.75">
+      <c r="A18" s="18">
+        <v>115</v>
+      </c>
+      <c r="B18" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="18">
         <v>0.66</v>
       </c>
-      <c r="E18" s="23">
-        <v>645.0</v>
-      </c>
-      <c r="F18" s="24">
-        <f t="shared" si="2"/>
-        <v>425.7</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="22"/>
-      <c r="B19" s="25" t="s">
+      <c r="E18" s="18">
+        <v>645</v>
+      </c>
+      <c r="F18" s="20">
+        <f>D18*E18</f>
+        <v>425.70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="12.75">
+      <c r="A19" s="19"/>
+      <c r="B19" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="24">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="20">
         <f>SUM(F14:F18)</f>
         <v>1106.73</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="22"/>
-      <c r="B20" s="25" t="s">
+    <row r="20" spans="1:6" ht="12.75">
+      <c r="A20" s="19"/>
+      <c r="B20" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="26"/>
-      <c r="D20" s="26"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="24">
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="20">
         <f>F19*0.01</f>
-        <v>11.0673</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="22"/>
-      <c r="B21" s="25" t="s">
+        <v>11.067299999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="12.75">
+      <c r="A21" s="19"/>
+      <c r="B21" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="26"/>
-      <c r="D21" s="26"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="24">
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="20">
         <f>SUM(F19:F20)</f>
         <v>1117.7973</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="22"/>
-      <c r="B22" s="25" t="s">
+    <row r="22" spans="1:6" ht="12.75">
+      <c r="A22" s="19"/>
+      <c r="B22" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="24">
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="20">
         <f>F21*0.15</f>
-        <v>167.669595</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="22"/>
-      <c r="B23" s="25" t="s">
+        <v>167.66959499999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="12.75">
+      <c r="A23" s="19"/>
+      <c r="B23" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="24">
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="20">
         <f>SUM(F21:F22)</f>
         <v>1285.466895</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="22"/>
-      <c r="B24" s="25" t="s">
+    <row r="24" spans="1:6" ht="12.75">
+      <c r="A24" s="19"/>
+      <c r="B24" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C24" s="26"/>
-      <c r="D24" s="26"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="24">
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="20">
         <f>F23</f>
         <v>1285.466895</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="22"/>
-      <c r="B25" s="25" t="s">
+    <row r="25" spans="1:6" ht="12.75">
+      <c r="A25" s="19"/>
+      <c r="B25" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="18">
-        <f>round(F24/10,2)</f>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="16">
+        <f>ROUND(F24/10,2)</f>
         <v>128.55</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="28" t="str">
+    <row r="26" spans="1:6" ht="12.75">
+      <c r="A26" s="22" t="str">
         <f>CONCATENATE("Say ₹ ",F13," + ",F25," x Cost Index")</f>
         <v>Say ₹ 634.47 + 128.55 x Cost Index</v>
       </c>
@@ -989,11 +1177,11 @@
       <c r="E26" s="2"/>
       <c r="F26" s="3"/>
     </row>
-    <row r="27">
-      <c r="A27" s="29">
-        <v>0.0</v>
-      </c>
-      <c r="B27" s="30" t="s">
+    <row r="27" spans="1:6" ht="12.75">
+      <c r="A27" s="23">
+        <v>0</v>
+      </c>
+      <c r="B27" s="24" t="s">
         <v>25</v>
       </c>
       <c r="C27" s="6"/>
@@ -1001,39 +1189,39 @@
       <c r="E27" s="6"/>
       <c r="F27" s="7"/>
     </row>
-    <row r="28">
-      <c r="A28" s="29" t="s">
+    <row r="28" spans="1:6" ht="12.75">
+      <c r="A28" s="23" t="s">
         <v>2</v>
       </c>
-      <c r="B28" s="29" t="s">
+      <c r="B28" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="D28" s="29" t="s">
+      <c r="D28" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="E28" s="29" t="s">
+      <c r="E28" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="31"/>
-      <c r="B29" s="32" t="s">
+    <row r="29" spans="1:6" ht="12.75">
+      <c r="A29" s="25"/>
+      <c r="B29" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="31"/>
-      <c r="F29" s="31"/>
-    </row>
-    <row r="30">
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+    </row>
+    <row r="30" spans="1:6" ht="12.75">
       <c r="A30" s="10"/>
-      <c r="B30" s="32" t="s">
+      <c r="B30" s="26" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="10"/>
@@ -1041,30 +1229,30 @@
       <c r="E30" s="10"/>
       <c r="F30" s="10"/>
     </row>
-    <row r="31">
-      <c r="A31" s="33" t="s">
+    <row r="31" spans="1:6" ht="12.75">
+      <c r="A31" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="35" t="s">
+      <c r="C31" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="D31" s="35">
-        <v>11.5</v>
-      </c>
-      <c r="E31" s="33">
-        <v>150.0</v>
-      </c>
-      <c r="F31" s="36">
+      <c r="D31" s="27">
+        <v>11.50</v>
+      </c>
+      <c r="E31" s="27">
+        <v>150</v>
+      </c>
+      <c r="F31" s="28">
         <f>D31*E31</f>
         <v>1725</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:6" ht="12.75">
       <c r="A32" s="10"/>
-      <c r="B32" s="32" t="s">
+      <c r="B32" s="26" t="s">
         <v>13</v>
       </c>
       <c r="C32" s="10"/>
@@ -1072,129 +1260,129 @@
       <c r="E32" s="10"/>
       <c r="F32" s="10"/>
     </row>
-    <row r="33">
-      <c r="A33" s="37"/>
-      <c r="B33" s="38" t="s">
+    <row r="33" spans="1:6" ht="12.75">
+      <c r="A33" s="29"/>
+      <c r="B33" s="30" t="s">
         <v>14</v>
       </c>
       <c r="C33" s="6"/>
       <c r="D33" s="6"/>
       <c r="E33" s="7"/>
-      <c r="F33" s="39">
+      <c r="F33" s="31">
         <f>F31*0.01</f>
         <v>17.25</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="37"/>
-      <c r="B34" s="38" t="s">
+    <row r="34" spans="1:6" ht="12.75">
+      <c r="A34" s="29"/>
+      <c r="B34" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="6"/>
       <c r="D34" s="6"/>
       <c r="E34" s="7"/>
-      <c r="F34" s="39">
+      <c r="F34" s="31">
         <f>SUM(F31:F33)</f>
         <v>1742.25</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="37"/>
-      <c r="B35" s="38" t="s">
+    <row r="35" spans="1:6" ht="12.75">
+      <c r="A35" s="29"/>
+      <c r="B35" s="30" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="6"/>
       <c r="D35" s="6"/>
       <c r="E35" s="7"/>
-      <c r="F35" s="39">
+      <c r="F35" s="31">
         <f>F34*0.15</f>
         <v>261.3375</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="37"/>
-      <c r="B36" s="38" t="s">
+    <row r="36" spans="1:6" ht="12.75">
+      <c r="A36" s="29"/>
+      <c r="B36" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C36" s="6"/>
       <c r="D36" s="6"/>
       <c r="E36" s="7"/>
-      <c r="F36" s="39">
+      <c r="F36" s="31">
         <f>SUM(F34:F35)</f>
-        <v>2003.5875</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="37"/>
-      <c r="B37" s="38" t="s">
+        <v>2003.5875000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="12.75">
+      <c r="A37" s="29"/>
+      <c r="B37" s="30" t="s">
         <v>17</v>
       </c>
       <c r="C37" s="6"/>
       <c r="D37" s="6"/>
       <c r="E37" s="7"/>
-      <c r="F37" s="39">
+      <c r="F37" s="31">
         <f>F36</f>
-        <v>2003.5875</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="37"/>
-      <c r="B38" s="38" t="s">
+        <v>2003.5875000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="12.75">
+      <c r="A38" s="29"/>
+      <c r="B38" s="30" t="s">
         <v>18</v>
       </c>
       <c r="C38" s="6"/>
       <c r="D38" s="6"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="40">
-        <f>round(F37/10,2)</f>
+      <c r="F38" s="32">
+        <f>ROUND(F37/10,2)</f>
         <v>200.36</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="37">
-        <v>116.0</v>
-      </c>
-      <c r="B39" s="32" t="s">
+    <row r="39" spans="1:6" ht="12.75">
+      <c r="A39" s="29">
+        <v>116</v>
+      </c>
+      <c r="B39" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="37" t="s">
+      <c r="C39" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="D39" s="37">
+      <c r="D39" s="29">
         <v>0.12</v>
       </c>
-      <c r="E39" s="41">
-        <v>784.0</v>
-      </c>
-      <c r="F39" s="39">
-        <f t="shared" ref="F39:F40" si="3">D39*E39</f>
+      <c r="E39" s="29">
+        <v>784</v>
+      </c>
+      <c r="F39" s="31">
+        <f>D39*E39</f>
         <v>94.08</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="35">
-        <v>114.0</v>
-      </c>
-      <c r="B40" s="32" t="s">
+    <row r="40" spans="1:6" ht="12.75">
+      <c r="A40" s="27">
+        <v>114</v>
+      </c>
+      <c r="B40" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="C40" s="35" t="s">
+      <c r="C40" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D40" s="35">
+      <c r="D40" s="27">
         <v>0.25</v>
       </c>
-      <c r="E40" s="33">
-        <v>645.0</v>
-      </c>
-      <c r="F40" s="42">
-        <f t="shared" si="3"/>
+      <c r="E40" s="27">
+        <v>645</v>
+      </c>
+      <c r="F40" s="33">
+        <f>D40*E40</f>
         <v>161.25</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:6" ht="12.75">
       <c r="A41" s="10"/>
-      <c r="B41" s="32" t="s">
+      <c r="B41" s="26" t="s">
         <v>22</v>
       </c>
       <c r="C41" s="10"/>
@@ -1202,141 +1390,141 @@
       <c r="E41" s="10"/>
       <c r="F41" s="10"/>
     </row>
-    <row r="42">
-      <c r="A42" s="35">
-        <v>114.0</v>
-      </c>
-      <c r="B42" s="31" t="s">
+    <row r="42" spans="1:6" ht="12.75">
+      <c r="A42" s="27">
+        <v>114</v>
+      </c>
+      <c r="B42" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="C42" s="35" t="s">
+      <c r="C42" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="35">
+      <c r="D42" s="27">
         <v>0.66</v>
       </c>
-      <c r="E42" s="33">
-        <v>645.0</v>
-      </c>
-      <c r="F42" s="42">
-        <f t="shared" ref="F42:F43" si="4">D42*E42</f>
-        <v>425.7</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="43">
-        <v>115.0</v>
-      </c>
-      <c r="B43" s="44" t="s">
+      <c r="E42" s="27">
+        <v>645</v>
+      </c>
+      <c r="F42" s="33">
+        <f>D42*E42</f>
+        <v>425.70</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="12.75">
+      <c r="A43" s="34">
+        <v>115</v>
+      </c>
+      <c r="B43" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="C43" s="43" t="s">
+      <c r="C43" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="43">
+      <c r="D43" s="34">
         <v>0.66</v>
       </c>
-      <c r="E43" s="45">
-        <v>645.0</v>
-      </c>
-      <c r="F43" s="46">
-        <f t="shared" si="4"/>
-        <v>425.7</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="44"/>
-      <c r="B44" s="47" t="s">
+      <c r="E43" s="34">
+        <v>645</v>
+      </c>
+      <c r="F43" s="36">
+        <f>D43*E43</f>
+        <v>425.70</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="12.75">
+      <c r="A44" s="35"/>
+      <c r="B44" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="C44" s="26"/>
-      <c r="D44" s="26"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="46">
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="36">
         <f>SUM(F39:F43)</f>
         <v>1106.73</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="44"/>
-      <c r="B45" s="47" t="s">
+    <row r="45" spans="1:6" ht="12.75">
+      <c r="A45" s="35"/>
+      <c r="B45" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="C45" s="26"/>
-      <c r="D45" s="26"/>
-      <c r="E45" s="27"/>
-      <c r="F45" s="46">
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="36">
         <f>F44*0.01</f>
-        <v>11.0673</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="44"/>
-      <c r="B46" s="47" t="s">
+        <v>11.067299999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="12.75">
+      <c r="A46" s="35"/>
+      <c r="B46" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="26"/>
-      <c r="D46" s="26"/>
-      <c r="E46" s="27"/>
-      <c r="F46" s="46">
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="3"/>
+      <c r="F46" s="36">
         <f>SUM(F44:F45)</f>
         <v>1117.7973</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="44"/>
-      <c r="B47" s="47" t="s">
+    <row r="47" spans="1:6" ht="12.75">
+      <c r="A47" s="35"/>
+      <c r="B47" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="27"/>
-      <c r="F47" s="46">
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="3"/>
+      <c r="F47" s="36">
         <f>F46*0.15</f>
-        <v>167.669595</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="44"/>
-      <c r="B48" s="47" t="s">
+        <v>167.66959499999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="12.75">
+      <c r="A48" s="35"/>
+      <c r="B48" s="37" t="s">
         <v>15</v>
       </c>
-      <c r="C48" s="26"/>
-      <c r="D48" s="26"/>
-      <c r="E48" s="27"/>
-      <c r="F48" s="46">
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="36">
         <f>SUM(F46:F47)</f>
         <v>1285.466895</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="44"/>
-      <c r="B49" s="47" t="s">
+    <row r="49" spans="1:6" ht="12.75">
+      <c r="A49" s="35"/>
+      <c r="B49" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C49" s="26"/>
-      <c r="D49" s="26"/>
-      <c r="E49" s="27"/>
-      <c r="F49" s="46">
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="3"/>
+      <c r="F49" s="36">
         <f>F48</f>
         <v>1285.466895</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="44"/>
-      <c r="B50" s="47" t="s">
+    <row r="50" spans="1:6" ht="12.75">
+      <c r="A50" s="35"/>
+      <c r="B50" s="37" t="s">
         <v>18</v>
       </c>
-      <c r="C50" s="26"/>
-      <c r="D50" s="26"/>
-      <c r="E50" s="27"/>
-      <c r="F50" s="40">
-        <f>round(F49/10,2)</f>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="32">
+        <f>ROUND(F49/10,2)</f>
         <v>128.55</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="48" t="str">
+    <row r="51" spans="1:6" ht="12.75">
+      <c r="A51" s="38" t="str">
         <f>CONCATENATE("Say ₹ ",F38," + ",F50," x Cost Index")</f>
         <v>Say ₹ 200.36 + 128.55 x Cost Index</v>
       </c>
@@ -1410,9 +1598,6 @@
     <mergeCell ref="D31:D32"/>
     <mergeCell ref="E31:E32"/>
   </mergeCells>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/GWD Data/PVC With Trench.xlsx
+++ b/GWD Data/PVC With Trench.xlsx
@@ -806,7 +806,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96A751D6-6F22-48F9-BA03-042F37A8B9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ED2692D-50E3-4107-AA41-ACDC818EB9A6}">
   <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/GWD Data/PVC With Trench.xlsx
+++ b/GWD Data/PVC With Trench.xlsx
@@ -806,7 +806,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2ED2692D-50E3-4107-AA41-ACDC818EB9A6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{688E0985-18B6-4490-BC76-133047B9B9A6}">
   <dimension ref="A1:F51"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
